--- a/data/trans_orig/IP04F-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP04F-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58872</t>
+          <t>58349</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71676</t>
+          <t>71794</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63756</t>
+          <t>63172</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76008</t>
+          <t>75696</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>126912</t>
+          <t>127116</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144705</t>
+          <t>144839</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,09%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16411</t>
+          <t>16293</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29215</t>
+          <t>29738</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12348</t>
+          <t>12660</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24600</t>
+          <t>25184</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31737</t>
+          <t>31603</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49530</t>
+          <t>49326</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71934</t>
+          <t>72772</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83548</t>
+          <t>84159</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71187</t>
+          <t>70691</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84410</t>
+          <t>84519</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>148567</t>
+          <t>148579</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>165146</t>
+          <t>165247</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,31%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20541</t>
+          <t>19703</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12368</t>
+          <t>12259</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25591</t>
+          <t>26087</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24108</t>
+          <t>24007</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40687</t>
+          <t>40675</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73667</t>
+          <t>72945</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82210</t>
+          <t>81971</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80144</t>
+          <t>80227</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85616</t>
+          <t>85621</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>156164</t>
+          <t>157276</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>166409</t>
+          <t>166972</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12490</t>
+          <t>13212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16236</t>
+          <t>15124</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>186265</t>
+          <t>185912</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>197557</t>
+          <t>197029</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>209528</t>
+          <t>208787</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>220277</t>
+          <t>219829</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>399513</t>
+          <t>399903</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>414561</t>
+          <t>414832</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7099</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18391</t>
+          <t>18744</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17481</t>
+          <t>18222</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17105</t>
+          <t>16834</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32153</t>
+          <t>31763</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>132810</t>
+          <t>132281</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>142084</t>
+          <t>141915</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>125374</t>
+          <t>125736</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>135867</t>
+          <t>136340</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>262723</t>
+          <t>261852</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>276155</t>
+          <t>276217</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13787</t>
+          <t>14316</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24144</t>
+          <t>25015</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43441</t>
+          <t>43371</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50519</t>
+          <t>50539</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62256</t>
+          <t>62974</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70604</t>
+          <t>70642</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>109303</t>
+          <t>108926</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>119835</t>
+          <t>119490</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9776</t>
+          <t>9846</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11782</t>
+          <t>11064</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7421</t>
+          <t>7766</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17953</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>588053</t>
+          <t>587432</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>613943</t>
+          <t>613695</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>634369</t>
+          <t>634690</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>658232</t>
+          <t>659590</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1230036</t>
+          <t>1231713</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1266475</t>
+          <t>1266384</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>57247</t>
+          <t>57495</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>83137</t>
+          <t>83758</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>54462</t>
+          <t>53104</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>78325</t>
+          <t>78004</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>117409</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>153848</t>
+          <t>152171</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60203</t>
+          <t>59900</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71683</t>
+          <t>71965</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77229</t>
+          <t>76416</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>88799</t>
+          <t>89128</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>140597</t>
+          <t>140635</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158151</t>
+          <t>158201</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,72%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10938</t>
+          <t>10656</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22418</t>
+          <t>22721</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10998</t>
+          <t>10669</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22568</t>
+          <t>23381</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24267</t>
+          <t>24217</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41821</t>
+          <t>41783</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82310</t>
+          <t>82161</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>94458</t>
+          <t>94488</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89478</t>
+          <t>88570</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101607</t>
+          <t>101560</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>176234</t>
+          <t>176600</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>193623</t>
+          <t>193772</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10681</t>
+          <t>10651</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22829</t>
+          <t>22978</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10469</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22598</t>
+          <t>23506</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23592</t>
+          <t>23443</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40981</t>
+          <t>40615</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50577</t>
+          <t>50570</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58071</t>
+          <t>58303</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64883</t>
+          <t>65061</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71559</t>
+          <t>71565</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>118256</t>
+          <t>117791</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>128498</t>
+          <t>128507</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>10721</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8613</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>16996</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>206063</t>
+          <t>204490</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>215876</t>
+          <t>215416</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>187549</t>
+          <t>187696</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>199515</t>
+          <t>199825</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>398119</t>
+          <t>397896</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>413029</t>
+          <t>413033</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16345</t>
+          <t>17918</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9277</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21243</t>
+          <t>21096</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18171</t>
+          <t>18167</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33081</t>
+          <t>33304</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>122474</t>
+          <t>122642</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>131316</t>
+          <t>131514</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>132205</t>
+          <t>132698</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>139641</t>
+          <t>139726</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>257937</t>
+          <t>259018</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>269381</t>
+          <t>270183</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12527</t>
+          <t>12359</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9449</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7273</t>
+          <t>6471</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18717</t>
+          <t>17636</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51501</t>
+          <t>51726</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58847</t>
+          <t>58749</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61412</t>
+          <t>60725</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>115499</t>
+          <t>115495</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>124387</t>
+          <t>124368</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9586</t>
+          <t>9361</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3882</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12751</t>
+          <t>12755</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>592975</t>
+          <t>593323</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>617076</t>
+          <t>618249</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>632554</t>
+          <t>633010</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>655686</t>
+          <t>657016</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1234997</t>
+          <t>1234547</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1268877</t>
+          <t>1267340</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>50470</t>
+          <t>49297</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>74571</t>
+          <t>74223</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>47291</t>
+          <t>45961</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>70423</t>
+          <t>69967</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>101646</t>
+          <t>103183</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>135526</t>
+          <t>135976</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP04F-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP04F-Clase-trans_orig.xlsx
@@ -542,7 +542,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -553,7 +553,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -721,72 +721,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>70182</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>63041</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>75599</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>79,43%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>71,35%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>85,56%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>65891</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>58349</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>71794</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>59365</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>72069</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>74,8%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>66,24%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>81,5%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>70182</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>63172</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>75696</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>79,43%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>127116</t>
+          <t>125572</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144839</t>
+          <t>144727</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,03%</t>
         </is>
       </c>
     </row>
@@ -834,72 +834,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18174</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12757</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25315</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>20,57%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>14,44%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>28,65%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>22196</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16293</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>29738</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16018</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>28722</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>25,2%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18,5%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>33,76%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18174</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12660</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>25184</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>20,57%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31603</t>
+          <t>31715</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49326</t>
+          <t>50870</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -952,52 +952,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>88356</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>88356</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>88356</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>88087</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88087</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88087</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>88356</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>88356</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>88356</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1064,72 +1064,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>78540</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>71467</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>84765</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>81,15%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>73,85%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>87,59%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>79021</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>72772</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>84159</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>72608</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>84512</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>85,45%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>78,69%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>91,01%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>78540</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>70691</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>84519</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>81,15%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>148579</t>
+          <t>148038</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>165247</t>
+          <t>164932</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,15%</t>
         </is>
       </c>
     </row>
@@ -1177,72 +1177,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18238</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12013</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>25311</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>18,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>12,41%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>26,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>13454</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8316</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19703</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7963</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>19867</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>14,55%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,99%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>21,31%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>18238</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>12259</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>26087</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>18,85%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24007</t>
+          <t>24322</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40675</t>
+          <t>41216</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -1290,57 +1290,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>96778</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96778</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>96778</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>92475</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>92475</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>92475</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>96778</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>96778</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96778</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1407,72 +1407,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>84154</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>80553</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>85618</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>93,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>99,28%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>78442</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>72945</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>81971</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>72865</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>82064</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>91,05%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>84,66%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>95,14%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>84154</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>80227</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>85621</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157276</t>
+          <t>156210</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>166972</t>
+          <t>166772</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -1520,72 +1520,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6,6%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>7715</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4186</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>13212</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4093</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>13292</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>8,95%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>15,34%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2088</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>6015</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15124</t>
+          <t>16190</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -1633,57 +1633,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>86242</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>86242</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86242</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>86157</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>86157</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>86157</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>86242</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>86242</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>86242</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1750,72 +1750,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>215537</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>208964</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>220102</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>94,95%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>92,05%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>96,96%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>192539</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>185912</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>197029</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>186245</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>94,08%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>90,84%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>208787</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>219829</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>94,95%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>399903</t>
+          <t>399520</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>414832</t>
+          <t>414612</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -1863,72 +1863,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11472</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6907</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>18045</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7,95%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>12117</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>7627</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>18744</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>7343</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>18411</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>5,92%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>11472</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>7180</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>18222</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31763</t>
+          <t>32146</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -1976,57 +1976,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>227009</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>227009</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>227009</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>297</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>204656</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>204656</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>204656</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>227009</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>227009</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>227009</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2093,72 +2093,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>131828</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>126119</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>136073</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>93,98%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>89,91%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>97,01%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>138333</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>132281</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>141915</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>132887</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>142159</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>94,36%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>90,23%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>96,81%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>131828</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>125736</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>136340</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>93,98%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>261852</t>
+          <t>262686</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>276217</t>
+          <t>275689</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -2206,72 +2206,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8442</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14151</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>10,09%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>8264</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>4682</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>14316</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>4438</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>13710</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>5,64%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>8442</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3930</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>14534</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25015</t>
+          <t>24181</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -2319,57 +2319,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>140270</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>140270</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>140270</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>146597</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>146597</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>146597</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>140270</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>140270</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>140270</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2436,72 +2436,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>67371</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>62540</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>70539</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>91,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>84,47%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>95,27%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>47782</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>43371</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>50539</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>43517</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>50673</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>89,79%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>81,5%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>94,97%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>67371</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>62974</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>70642</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>91,0%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>108926</t>
+          <t>108994</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>119490</t>
+          <t>119861</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -2549,72 +2549,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6667</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3499</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>11498</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>9,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>15,53%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>5435</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2678</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>9846</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2544</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>9700</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>10,21%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>18,5%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>6667</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>3396</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>11064</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>9,0%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7766</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18330</t>
+          <t>18262</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -2662,57 +2662,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53217</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53217</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53217</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2779,107 +2779,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>647613</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>633603</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>660059</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>90,87%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>88,9%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>92,61%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>871</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>602010</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>587432</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>613695</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>587085</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>613923</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>89,69%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>87,52%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>91,43%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>647613</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>634690</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>659590</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>90,87%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>87,47%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>91,47%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1796</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1249623</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>1232502</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>1267603</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>90,3%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>89,06%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>92,55%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1796</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1249623</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1231713</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1266384</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>90,3%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>89,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,6%</t>
         </is>
       </c>
     </row>
@@ -2892,107 +2892,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>65081</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>52635</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>79091</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>9,13%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>7,39%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>69180</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>57495</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>83758</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>57267</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>84105</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>10,31%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>12,48%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>65081</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>53104</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>78004</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>9,13%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>12,53%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>134261</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>116281</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>151382</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>9,7%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>8,4%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>10,94%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>134261</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>117500</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>152171</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>8,49%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -3005,57 +3005,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>712694</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>712694</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>712694</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>971</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>671190</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>671190</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>671190</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>712694</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>712694</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>712694</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3188,7 +3188,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>83665</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>76594</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>88812</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>83,84%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>76,75%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>88,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>66484</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>59900</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>71965</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>60441</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>71519</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>80,47%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>72,5%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>87,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>83665</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>76416</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>89128</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>83,84%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>140635</t>
+          <t>141080</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158201</t>
+          <t>157780</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,49%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16132</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10985</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23203</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16,16%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>11,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>23,25%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>16137</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10656</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>22721</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11102</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>22180</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>19,53%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>27,5%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16132</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>10669</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>23381</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>16,16%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24217</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41783</t>
+          <t>41338</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>82621</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>82621</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>82621</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>96156</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>88620</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>101054</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>85,8%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>79,07%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>90,17%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>89568</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>82161</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>94488</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>82944</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>94702</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>85,19%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>78,15%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>89,87%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>96156</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>88570</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>101560</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>85,8%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>176600</t>
+          <t>176795</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>193772</t>
+          <t>193446</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,06%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15920</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11022</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23456</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>14,2%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9,83%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>20,93%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>15571</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10651</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22978</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>10437</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>22195</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>14,81%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,13%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>21,85%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>15920</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>10516</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>23506</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>14,2%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23443</t>
+          <t>23769</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40615</t>
+          <t>40420</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112076</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112076</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112076</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>105139</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>105139</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>105139</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>112076</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>112076</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>112076</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>68987</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>64631</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>71538</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>93,87%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>87,94%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>97,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>55078</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>50570</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>58303</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>50308</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>58414</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>89,86%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>82,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>68987</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>65061</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>71565</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>93,87%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117791</t>
+          <t>118219</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>128507</t>
+          <t>128438</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4509</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1958</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8865</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>12,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>6213</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2988</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10721</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2877</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>10983</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>10,14%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>17,49%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4509</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1931</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>8435</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>6,13%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6280</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16996</t>
+          <t>16568</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>73496</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>73496</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>73496</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>61291</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>61291</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>61291</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>73496</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>73496</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>73496</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>194572</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>187499</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>199654</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>93,19%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>89,8%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>95,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>321</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>211509</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>204490</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>215416</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>205899</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>215823</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>95,1%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>91,94%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>96,86%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>194572</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>187696</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>199825</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>93,19%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>397896</t>
+          <t>397275</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>413033</t>
+          <t>412946</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -4498,72 +4498,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>14220</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9138</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>21293</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>10899</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6992</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>17918</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>6585</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>16509</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>4,9%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,06%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>14220</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>8967</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>21096</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18167</t>
+          <t>18254</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33304</t>
+          <t>33925</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -4611,57 +4611,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>208792</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>208792</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>208792</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>339</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>222408</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>222408</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>222408</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>208792</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>208792</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>208792</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>137011</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>132576</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>139699</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>96,72%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>93,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>98,62%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>127947</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>122642</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>131514</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>122568</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>131626</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>94,78%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>90,85%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>137011</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>132698</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>139726</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>96,72%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>259018</t>
+          <t>258801</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>270183</t>
+          <t>269448</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -4841,72 +4841,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4643</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>9078</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>7054</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>3487</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>12359</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3375</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>12433</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>5,22%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>9,15%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>4643</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1928</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>8956</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6471</t>
+          <t>7206</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17636</t>
+          <t>17853</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -4954,57 +4954,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>141654</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>141654</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>141654</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>135001</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>135001</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>135001</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>141654</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>141654</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>141654</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>64969</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>61348</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>66445</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>91,34%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>98,93%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>55947</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>51726</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>58749</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>51627</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>58709</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>91,59%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>84,68%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>96,17%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>64969</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>60725</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>66445</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>96,73%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>115495</t>
+          <t>115724</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>124368</t>
+          <t>124645</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -5184,72 +5184,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5815</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>8,66%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>5140</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2338</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>9361</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2378</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>9460</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>8,41%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>15,32%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>6438</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12755</t>
+          <t>12526</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -5297,57 +5297,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67163</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67163</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67163</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67163</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67163</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67163</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5414,72 +5414,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>645360</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>632471</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>656278</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>91,8%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>89,97%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>93,36%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>606533</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>593323</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>618249</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>593011</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>617374</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>90,86%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>88,88%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>92,62%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>645360</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>633010</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>657016</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>91,8%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1234547</t>
+          <t>1234761</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1267340</t>
+          <t>1268393</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -5527,72 +5527,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>57617</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>46699</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>70506</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>8,2%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>6,64%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>10,03%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>61013</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>49297</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>74223</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>50172</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>74535</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>9,14%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>11,12%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>57617</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>45961</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>69967</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>8,2%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>103183</t>
+          <t>102130</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>135976</t>
+          <t>135762</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -5640,57 +5640,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>702977</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>702977</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>702977</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1006</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>667546</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>667546</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>667546</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1007</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>702977</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>702977</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>702977</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
